--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -132,15 +137,6 @@
   </si>
   <si>
     <t>杀敌道攻</t>
-  </si>
-  <si>
-    <t>万敌攻增</t>
-  </si>
-  <si>
-    <t>万敌血增</t>
-  </si>
-  <si>
-    <t>万敌防增</t>
   </si>
 </sst>
 </file>
@@ -330,7 +326,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,12 +342,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,7 +662,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -696,16 +686,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -714,96 +704,95 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1123,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O26"/>
+  <dimension ref="C1:O29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1689,7 +1678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:14">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="2">
         <v>12</v>
       </c>
@@ -1711,10 +1700,10 @@
       <c r="I17" s="2">
         <v>1</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="2">
         <v>20</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="2">
         <v>40</v>
       </c>
       <c r="L17" s="2">
@@ -1727,7 +1716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1765,7 +1754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1803,7 +1792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1841,7 +1830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1879,7 +1868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1917,89 +1906,275 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C23" s="1">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C23" s="2">
         <v>18</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>49</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>72</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="2">
         <v>3</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="2">
         <v>6</v>
       </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
         <v>15</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="2">
         <v>30</v>
       </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1">
-        <v>9</v>
-      </c>
-      <c r="N23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="L23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2">
+        <v>9</v>
+      </c>
+      <c r="N23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1">
+        <v>73</v>
+      </c>
+      <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>20</v>
+      </c>
+      <c r="J24" s="1">
+        <v>15</v>
+      </c>
+      <c r="K24" s="1">
+        <v>45</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>9</v>
+      </c>
+      <c r="N24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1">
+        <v>73</v>
+      </c>
+      <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="H25" s="1">
+        <v>3</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>15</v>
+      </c>
+      <c r="K25" s="1">
+        <v>45</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>9</v>
+      </c>
+      <c r="N25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="E26" s="1">
+        <v>73</v>
+      </c>
+      <c r="F26" s="1">
+        <v>73</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>15</v>
+      </c>
+      <c r="K26" s="1">
+        <v>45</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1">
+        <v>9</v>
+      </c>
+      <c r="N26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="1">
+        <v>73</v>
+      </c>
+      <c r="F27" s="1">
+        <v>73</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>4</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>10</v>
+      </c>
+      <c r="K27" s="1">
+        <v>30</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
+        <v>9</v>
+      </c>
+      <c r="N27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1">
+        <v>73</v>
+      </c>
+      <c r="F28" s="1">
+        <v>73</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>10</v>
+      </c>
+      <c r="K28" s="1">
+        <v>30</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>9</v>
+      </c>
+      <c r="N28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="1">
+        <v>73</v>
+      </c>
+      <c r="F29" s="1">
+        <v>73</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3</v>
+      </c>
+      <c r="H29" s="2">
+        <v>6</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>10</v>
+      </c>
+      <c r="K29" s="2">
+        <v>30</v>
+      </c>
+      <c r="L29" s="2">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2">
+        <v>9</v>
+      </c>
+      <c r="N29" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 E4 F4 E5:F5 O3:O5 C3:D5 G3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -121,10 +121,10 @@
     <t>string</t>
   </si>
   <si>
+    <t>杀敌生命</t>
+  </si>
+  <si>
     <t>杀敌攻击</t>
-  </si>
-  <si>
-    <t>杀敌生命</t>
   </si>
   <si>
     <t>杀敌防御</t>
